--- a/branches/main/ValueSet-mii-vs-icu-body-site-observation-beatmung.xlsx
+++ b/branches/main/ValueSet-mii-vs-icu-body-site-observation-beatmung.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.3</t>
+    <t>2027.0.0-ballot.3-rc.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>Concept</t>
-  </si>
-  <si>
-    <t>11527006</t>
   </si>
   <si>
     <t>89187006</t>
@@ -381,7 +378,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -412,22 +409,16 @@
       <c r="A4" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>31</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
